--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,219 +396,219 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>236</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>75</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>165</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>173</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>173</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>146</v>
+        <v>307</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>170</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>151</v>
+        <v>361</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>205</v>
+        <v>411</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>118</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>305</v>
+        <v>944</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>336</v>
+        <v>947</v>
       </c>
       <c r="B14">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>123</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>414</v>
+        <v>950</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>418</v>
+        <v>990</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>153</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>436</v>
+        <v>1504</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>523</v>
+        <v>2049</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>624</v>
+        <v>2050</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>113</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>947</v>
+        <v>2055</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>46</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>976</v>
+        <v>2103</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C21">
         <v>7</v>
@@ -616,585 +616,332 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1243</v>
+        <v>2188</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>111</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1409</v>
+        <v>2422</v>
       </c>
       <c r="B23">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1413</v>
+        <v>2423</v>
       </c>
       <c r="B24">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>114</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1656</v>
+        <v>2436</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1814</v>
+        <v>2497</v>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2050</v>
+        <v>2774</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2054</v>
+        <v>2775</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>518</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2331</v>
+        <v>2859</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C29">
-        <v>134</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2423</v>
+        <v>2934</v>
       </c>
       <c r="B30">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2497</v>
+        <v>3429</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2774</v>
+        <v>3495</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>184</v>
+        <v>643</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2859</v>
+        <v>3674</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>3429</v>
+        <v>4232</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C34">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>3495</v>
+        <v>5490</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>1108</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>3598</v>
+        <v>6360</v>
       </c>
       <c r="B36">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>3670</v>
+        <v>8216</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>4927</v>
+        <v>8648</v>
       </c>
       <c r="B38">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>86</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>5490</v>
+        <v>8650</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>5584</v>
+        <v>9786</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>272</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>5585</v>
+        <v>9877</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C41">
-        <v>266</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>5647</v>
+        <v>10149</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>68</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>6158</v>
+        <v>11396</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>6496</v>
+        <v>11685</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>6935</v>
+        <v>11737</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>7007</v>
+        <v>11738</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>89</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>7886</v>
+        <v>11836</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>157</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>8156</v>
+        <v>12923</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>8356</v>
+        <v>12924</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>98</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>8672</v>
+        <v>23234</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>315</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>8915</v>
+        <v>23994</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52">
-        <v>9507</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
-      </c>
-      <c r="C52">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53">
-        <v>9784</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54">
-        <v>9877</v>
-      </c>
-      <c r="B54">
-        <v>15</v>
-      </c>
-      <c r="C54">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55">
-        <v>10149</v>
-      </c>
-      <c r="B55">
-        <v>3</v>
-      </c>
-      <c r="C55">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56">
-        <v>10716</v>
-      </c>
-      <c r="B56">
-        <v>3</v>
-      </c>
-      <c r="C56">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57">
-        <v>11681</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58">
-        <v>11683</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59">
-        <v>11685</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60">
-        <v>11773</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61">
-        <v>11961</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62">
-        <v>11962</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63">
-        <v>12040</v>
-      </c>
-      <c r="B63">
-        <v>68</v>
-      </c>
-      <c r="C63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64">
-        <v>12304</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65">
-        <v>13034</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
-      </c>
-      <c r="C65">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66">
-        <v>13200</v>
-      </c>
-      <c r="B66">
-        <v>10</v>
-      </c>
-      <c r="C66">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67">
-        <v>13928</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68">
-        <v>19980</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69">
-        <v>21454</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
-        <v>22573</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71">
-        <v>23238</v>
-      </c>
-      <c r="B71">
-        <v>29</v>
-      </c>
-      <c r="C71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72">
-        <v>24567</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73">
-        <v>24668</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74">
-        <v>25278</v>
-      </c>
-      <c r="B74">
-        <v>2</v>
-      </c>
-      <c r="C74">
-        <v>306</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -407,95 +407,95 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>538</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>144</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -506,472 +506,472 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>75</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>34</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>141</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>344</v>
+        <v>378</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>13</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>362</v>
+        <v>413</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>378</v>
+        <v>417</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>414</v>
+        <v>523</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>416</v>
+        <v>589</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>418</v>
+        <v>788</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>69</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>523</v>
+        <v>944</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>583</v>
+        <v>950</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>589</v>
+        <v>976</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>616</v>
+        <v>1006</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>48</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>624</v>
+        <v>1055</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>788</v>
+        <v>1124</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>944</v>
+        <v>1134</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>950</v>
+        <v>1413</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>976</v>
+        <v>1429</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1006</v>
+        <v>1448</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1055</v>
+        <v>1490</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1124</v>
+        <v>1504</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1134</v>
+        <v>1654</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1413</v>
+        <v>1656</v>
       </c>
       <c r="B41">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1429</v>
+        <v>2188</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>125</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1490</v>
+        <v>2190</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1654</v>
+        <v>2193</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1656</v>
+        <v>2194</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2190</v>
+        <v>2203</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2193</v>
+        <v>2217</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2194</v>
+        <v>2265</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2203</v>
+        <v>2331</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2217</v>
+        <v>2419</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2267</v>
+        <v>2423</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2331</v>
+        <v>2436</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2423</v>
+        <v>2438</v>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>18</v>
+        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2436</v>
+        <v>2507</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -979,68 +979,68 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2438</v>
+        <v>2776</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>305</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2497</v>
+        <v>2778</v>
       </c>
       <c r="B56">
         <v>2</v>
       </c>
       <c r="C56">
-        <v>79</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2507</v>
+        <v>2805</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>137</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2774</v>
+        <v>2912</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2775</v>
+        <v>2934</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>67</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2776</v>
+        <v>2990</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>64</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1056,351 +1056,351 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3434</v>
+        <v>3021</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3477</v>
+        <v>3434</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3495</v>
+        <v>3477</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>500</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3674</v>
+        <v>3495</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>122</v>
+        <v>509</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>4043</v>
+        <v>3674</v>
       </c>
       <c r="B66">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>4232</v>
+        <v>3896</v>
       </c>
       <c r="B67">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C67">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>4926</v>
+        <v>4043</v>
       </c>
       <c r="B68">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C68">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5152</v>
+        <v>4232</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5153</v>
+        <v>4926</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5493</v>
+        <v>5152</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5584</v>
+        <v>5153</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>118</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5585</v>
+        <v>5490</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>122</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>5584</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>24</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6496</v>
+        <v>5585</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>19</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6540</v>
+        <v>5647</v>
       </c>
       <c r="B76">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6936</v>
+        <v>5733</v>
       </c>
       <c r="B77">
         <v>2</v>
       </c>
       <c r="C77">
-        <v>131</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7005</v>
+        <v>6097</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>75</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7007</v>
+        <v>6098</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C79">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7204</v>
+        <v>6158</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>18</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7887</v>
+        <v>6496</v>
       </c>
       <c r="B81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8285</v>
+        <v>6497</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>231</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8648</v>
+        <v>6540</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C83">
-        <v>173</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8650</v>
+        <v>7005</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>173</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8674</v>
+        <v>7007</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>138</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8853</v>
+        <v>7204</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>275</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8907</v>
+        <v>7520</v>
       </c>
       <c r="B87">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8915</v>
+        <v>7887</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C88">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8990</v>
+        <v>8285</v>
       </c>
       <c r="B89">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>34</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9085</v>
+        <v>8648</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>15</v>
+        <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9356</v>
+        <v>8650</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9358</v>
+        <v>8674</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>27</v>
+        <v>142</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9493</v>
+        <v>8907</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,131 +1408,131 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9784</v>
+        <v>8990</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9786</v>
+        <v>9085</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9841</v>
+        <v>9356</v>
       </c>
       <c r="B96">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>377</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9877</v>
+        <v>9357</v>
       </c>
       <c r="B97">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10149</v>
+        <v>9358</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>455</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10170</v>
+        <v>9493</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10181</v>
+        <v>9778</v>
       </c>
       <c r="B100">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10716</v>
+        <v>9784</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10993</v>
+        <v>9786</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10994</v>
+        <v>10170</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11090</v>
+        <v>10181</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11092</v>
+        <v>10716</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -1540,186 +1540,186 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11402</v>
+        <v>10993</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11681</v>
+        <v>10994</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>127</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11685</v>
+        <v>11090</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11738</v>
+        <v>11092</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11739</v>
+        <v>11402</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11773</v>
+        <v>11685</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11792</v>
+        <v>11738</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11812</v>
+        <v>11739</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11836</v>
+        <v>11773</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>122</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11838</v>
+        <v>11792</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>160</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11952</v>
+        <v>11812</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11962</v>
+        <v>11836</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>21</v>
+        <v>123</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12040</v>
+        <v>11838</v>
       </c>
       <c r="B118">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12048</v>
+        <v>11952</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>23</v>
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12128</v>
+        <v>11962</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12269</v>
+        <v>12040</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C121">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12294</v>
+        <v>12128</v>
       </c>
       <c r="B122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,120 +1727,120 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12546</v>
+        <v>12269</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12764</v>
+        <v>12294</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C124">
-        <v>358</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12923</v>
+        <v>12296</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C125">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12979</v>
+        <v>12764</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>20</v>
+        <v>349</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13114</v>
+        <v>12791</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13200</v>
+        <v>12923</v>
       </c>
       <c r="B128">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13928</v>
+        <v>12924</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>19980</v>
+        <v>12979</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>20556</v>
+        <v>13113</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>20977</v>
+        <v>13114</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>21088</v>
+        <v>13116</v>
       </c>
       <c r="B133">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>7</v>
@@ -1848,139 +1848,139 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21454</v>
+        <v>13200</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21793</v>
+        <v>13928</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>121</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21806</v>
+        <v>13962</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21810</v>
+        <v>13967</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>22364</v>
+        <v>19687</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>22665</v>
+        <v>19980</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>23234</v>
+        <v>20556</v>
       </c>
       <c r="B140">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>23235</v>
+        <v>21088</v>
       </c>
       <c r="B141">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C141">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23238</v>
+        <v>21454</v>
       </c>
       <c r="B142">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23380</v>
+        <v>21793</v>
       </c>
       <c r="B143">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23992</v>
+        <v>21806</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23994</v>
+        <v>21810</v>
       </c>
       <c r="B145">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24668</v>
+        <v>22364</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -1991,13 +1991,68 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
+        <v>22634</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>23234</v>
+      </c>
+      <c r="B148">
+        <v>29</v>
+      </c>
+      <c r="C148">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>23238</v>
+      </c>
+      <c r="B149">
+        <v>29</v>
+      </c>
+      <c r="C149">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>23992</v>
+      </c>
+      <c r="B150">
+        <v>29</v>
+      </c>
+      <c r="C150">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>24668</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
         <v>25960</v>
       </c>
-      <c r="B147">
-        <v>2</v>
-      </c>
-      <c r="C147">
-        <v>129</v>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -413,7 +413,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -424,7 +424,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -440,13 +440,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>268</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -479,23 +479,23 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -506,123 +506,123 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>154</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>116</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>523</v>
+        <v>583</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -638,13 +638,13 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -660,57 +660,57 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>976</v>
+        <v>947</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1006</v>
+        <v>976</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>114</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1055</v>
+        <v>1006</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1124</v>
+        <v>1055</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>89</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -726,13 +726,13 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B32">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -759,95 +759,95 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1450</v>
+        <v>1654</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>1656</v>
       </c>
       <c r="B36">
         <v>2</v>
       </c>
       <c r="C36">
-        <v>106</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1576</v>
+        <v>2099</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1654</v>
+        <v>2188</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1656</v>
+        <v>2190</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1668</v>
+        <v>2193</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1814</v>
+        <v>2194</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2099</v>
+        <v>2203</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2190</v>
+        <v>2217</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -858,18 +858,18 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2193</v>
+        <v>2265</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>16</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2194</v>
+        <v>2331</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -880,197 +880,197 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2203</v>
+        <v>2419</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2217</v>
+        <v>2422</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2267</v>
+        <v>2436</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2331</v>
+        <v>2438</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>304</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2418</v>
+        <v>2507</v>
       </c>
       <c r="B50">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2419</v>
+        <v>2778</v>
       </c>
       <c r="B51">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C51">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2422</v>
+        <v>2859</v>
       </c>
       <c r="B52">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2436</v>
+        <v>2934</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>56</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2438</v>
+        <v>2990</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>404</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2507</v>
+        <v>3016</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2776</v>
+        <v>3021</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C56">
-        <v>66</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2778</v>
+        <v>3434</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2912</v>
+        <v>3477</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2934</v>
+        <v>3495</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>14</v>
+        <v>523</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2990</v>
+        <v>3674</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>130</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2992</v>
+        <v>4232</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C61">
-        <v>130</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3016</v>
+        <v>4926</v>
       </c>
       <c r="B62">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="C62">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3021</v>
+        <v>5152</v>
       </c>
       <c r="B63">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,329 +1078,329 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3429</v>
+        <v>5153</v>
       </c>
       <c r="B64">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3430</v>
+        <v>5490</v>
       </c>
       <c r="B65">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3434</v>
+        <v>5493</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3477</v>
+        <v>5577</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>25</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3495</v>
+        <v>5584</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68">
-        <v>518</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>3549</v>
+        <v>5585</v>
       </c>
       <c r="B69">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>25</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>3598</v>
+        <v>5646</v>
       </c>
       <c r="B70">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>3674</v>
+        <v>5647</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3896</v>
+        <v>5648</v>
       </c>
       <c r="B72">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4043</v>
+        <v>5649</v>
       </c>
       <c r="B73">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>4926</v>
+        <v>5733</v>
       </c>
       <c r="B74">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5152</v>
+        <v>6158</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5153</v>
+        <v>6496</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5165</v>
+        <v>6540</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C77">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5490</v>
+        <v>6936</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>49</v>
+        <v>268</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5493</v>
+        <v>7005</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5577</v>
+        <v>7204</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5584</v>
+        <v>7520</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>122</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5585</v>
+        <v>7885</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>125</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>5647</v>
+        <v>7886</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>5649</v>
+        <v>7887</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>6097</v>
+        <v>8285</v>
       </c>
       <c r="B85">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>65</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>6158</v>
+        <v>8356</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>250</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>6496</v>
+        <v>8648</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>19</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>6540</v>
+        <v>8650</v>
       </c>
       <c r="B88">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>47</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>7005</v>
+        <v>8674</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>38</v>
+        <v>135</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>7007</v>
+        <v>8675</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>40</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>7204</v>
+        <v>8676</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>19</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>7520</v>
+        <v>8853</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>10</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8190</v>
+        <v>8907</v>
       </c>
       <c r="B93">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,73 +1408,73 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8285</v>
+        <v>8915</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>240</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8648</v>
+        <v>8923</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>173</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8907</v>
+        <v>8990</v>
       </c>
       <c r="B96">
         <v>29</v>
       </c>
       <c r="C96">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8923</v>
+        <v>9085</v>
       </c>
       <c r="B97">
         <v>29</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8990</v>
+        <v>9356</v>
       </c>
       <c r="B98">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9085</v>
+        <v>9357</v>
       </c>
       <c r="B99">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9356</v>
+        <v>9493</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1485,79 +1485,79 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9357</v>
+        <v>9778</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9493</v>
+        <v>9784</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9778</v>
+        <v>9786</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9784</v>
+        <v>9877</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C104">
-        <v>35</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>9786</v>
+        <v>10149</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105">
-        <v>45</v>
+        <v>458</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>9910</v>
+        <v>10170</v>
       </c>
       <c r="B106">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10170</v>
+        <v>10181</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -1573,13 +1573,13 @@
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>10980</v>
+        <v>10993</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="C111">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -1617,87 +1617,87 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11685</v>
+        <v>11234</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>252</v>
+        <v>88</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11738</v>
+        <v>11396</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11739</v>
+        <v>11681</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>28</v>
+        <v>254</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11773</v>
+        <v>11685</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11792</v>
+        <v>11737</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11812</v>
+        <v>11738</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11952</v>
+        <v>11739</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
-        <v>100</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12040</v>
+        <v>11773</v>
       </c>
       <c r="B120">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>7</v>
@@ -1705,21 +1705,21 @@
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12128</v>
+        <v>11792</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12294</v>
+        <v>11812</v>
       </c>
       <c r="B122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C122">
         <v>7</v>
@@ -1727,21 +1727,21 @@
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12296</v>
+        <v>11962</v>
       </c>
       <c r="B123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12579</v>
+        <v>12040</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C124">
         <v>7</v>
@@ -1749,216 +1749,216 @@
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12924</v>
+        <v>12128</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13041</v>
+        <v>12294</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C126">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13113</v>
+        <v>12296</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13114</v>
+        <v>12764</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13116</v>
+        <v>12791</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13200</v>
+        <v>12924</v>
       </c>
       <c r="B130">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13928</v>
+        <v>13113</v>
       </c>
       <c r="B131">
         <v>1</v>
       </c>
       <c r="C131">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13962</v>
+        <v>13114</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13967</v>
+        <v>13116</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>19980</v>
+        <v>13200</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C134">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>19982</v>
+        <v>13928</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19997</v>
+        <v>13962</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20556</v>
+        <v>19687</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21088</v>
+        <v>19980</v>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21454</v>
+        <v>19982</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21699</v>
+        <v>21088</v>
       </c>
       <c r="B140">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21806</v>
+        <v>21454</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21808</v>
+        <v>21793</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>232</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21810</v>
+        <v>21806</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22364</v>
+        <v>21810</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -1969,89 +1969,67 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22634</v>
+        <v>22364</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23238</v>
+        <v>22634</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C146">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23332</v>
+        <v>23234</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23539</v>
+        <v>23238</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23540</v>
+        <v>24669</v>
       </c>
       <c r="B149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>74</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24668</v>
+        <v>25960</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>24669</v>
-      </c>
-      <c r="B151">
-        <v>1</v>
-      </c>
-      <c r="C151">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>25960</v>
-      </c>
-      <c r="B152">
-        <v>2</v>
-      </c>
-      <c r="C152">
         <v>128</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -407,13 +407,13 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -462,211 +462,211 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>73</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>151</v>
+        <v>206</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>71</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>289</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>583</v>
+        <v>468</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>624</v>
+        <v>589</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>788</v>
+        <v>624</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>944</v>
+        <v>788</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -677,7 +677,7 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -699,7 +699,7 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -715,62 +715,62 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1134</v>
+        <v>1095</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1414</v>
+        <v>1134</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1429</v>
+        <v>1414</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1654</v>
+        <v>1448</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2099</v>
+        <v>1656</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2188</v>
+        <v>1814</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2190</v>
+        <v>2099</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>7</v>
@@ -814,18 +814,18 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2193</v>
+        <v>2188</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2194</v>
+        <v>2190</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -836,18 +836,18 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2217</v>
+        <v>2194</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -858,21 +858,21 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2265</v>
+        <v>2203</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>344</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2331</v>
+        <v>2212</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -880,175 +880,175 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2419</v>
+        <v>2217</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2422</v>
+        <v>2265</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>42</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2436</v>
+        <v>2331</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2438</v>
+        <v>2419</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C49">
-        <v>304</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2507</v>
+        <v>2436</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2778</v>
+        <v>2438</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>66</v>
+        <v>298</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2859</v>
+        <v>2507</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2934</v>
+        <v>2805</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="C53">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2990</v>
+        <v>2859</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C54">
-        <v>129</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3016</v>
+        <v>2934</v>
       </c>
       <c r="B55">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3021</v>
+        <v>2990</v>
       </c>
       <c r="B56">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3434</v>
+        <v>2992</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>43</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3477</v>
+        <v>3016</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C58">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3495</v>
+        <v>3434</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>523</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3674</v>
+        <v>3495</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>13</v>
+        <v>523</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4232</v>
+        <v>3598</v>
       </c>
       <c r="B61">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,21 +1056,21 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4926</v>
+        <v>3671</v>
       </c>
       <c r="B62">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5152</v>
+        <v>4232</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C63">
         <v>7</v>
@@ -1078,95 +1078,95 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5153</v>
+        <v>4926</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5490</v>
+        <v>5152</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5493</v>
+        <v>5153</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5577</v>
+        <v>5490</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>101</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5584</v>
+        <v>5491</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5585</v>
+        <v>5577</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5646</v>
+        <v>5584</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5647</v>
+        <v>5585</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5648</v>
+        <v>5646</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5649</v>
+        <v>5647</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1188,293 +1188,293 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>5648</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6158</v>
+        <v>5649</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>167</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6496</v>
+        <v>5733</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6540</v>
+        <v>6097</v>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C77">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6936</v>
+        <v>6098</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C78">
-        <v>268</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7005</v>
+        <v>6496</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7204</v>
+        <v>6540</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7520</v>
+        <v>6936</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>10</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7885</v>
+        <v>7005</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7886</v>
+        <v>7204</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7887</v>
+        <v>7520</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8285</v>
+        <v>7885</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C85">
-        <v>240</v>
+        <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8356</v>
+        <v>7886</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C86">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8648</v>
+        <v>7887</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C87">
-        <v>173</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8650</v>
+        <v>8190</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C88">
-        <v>173</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8674</v>
+        <v>8285</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>135</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8675</v>
+        <v>8648</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>136</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8676</v>
+        <v>8675</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8853</v>
+        <v>8676</v>
       </c>
       <c r="B92">
         <v>2</v>
       </c>
       <c r="C92">
-        <v>261</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8907</v>
+        <v>8853</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8915</v>
+        <v>8907</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8923</v>
+        <v>8915</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8990</v>
+        <v>8923</v>
       </c>
       <c r="B96">
         <v>29</v>
       </c>
       <c r="C96">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9085</v>
+        <v>8939</v>
       </c>
       <c r="B97">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C97">
-        <v>29</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9356</v>
+        <v>8990</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9357</v>
+        <v>9085</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C99">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9493</v>
+        <v>9356</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1485,35 +1485,35 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9778</v>
+        <v>9357</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9784</v>
+        <v>9493</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9786</v>
+        <v>9778</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -1524,67 +1524,67 @@
         <v>11</v>
       </c>
       <c r="C104">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10149</v>
+        <v>9910</v>
       </c>
       <c r="B105">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C105">
-        <v>458</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10170</v>
+        <v>10149</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C106">
-        <v>26</v>
+        <v>458</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10181</v>
+        <v>10170</v>
       </c>
       <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
         <v>26</v>
-      </c>
-      <c r="C107">
-        <v>65</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10716</v>
+        <v>10181</v>
       </c>
       <c r="B108">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C108">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>10993</v>
+        <v>10716</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C109">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>10994</v>
+        <v>10980</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -1595,21 +1595,21 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11090</v>
+        <v>10993</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11092</v>
+        <v>10994</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
         <v>7</v>
@@ -1617,142 +1617,142 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11234</v>
+        <v>11090</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11396</v>
+        <v>11092</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11681</v>
+        <v>11215</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11685</v>
+        <v>11234</v>
       </c>
       <c r="B116">
         <v>2</v>
       </c>
       <c r="C116">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11737</v>
+        <v>11396</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11738</v>
+        <v>11681</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11739</v>
+        <v>11685</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11773</v>
+        <v>11738</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11792</v>
+        <v>11773</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11812</v>
+        <v>11792</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11962</v>
+        <v>11812</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12040</v>
+        <v>11962</v>
       </c>
       <c r="B124">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12128</v>
+        <v>12040</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C125">
         <v>7</v>
@@ -1760,84 +1760,84 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12294</v>
+        <v>12128</v>
       </c>
       <c r="B126">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12296</v>
+        <v>12294</v>
       </c>
       <c r="B127">
         <v>4</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12764</v>
+        <v>12296</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>353</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12791</v>
+        <v>12546</v>
       </c>
       <c r="B129">
         <v>2</v>
       </c>
       <c r="C129">
-        <v>385</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12924</v>
+        <v>12764</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>25</v>
+        <v>355</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13113</v>
+        <v>12791</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13114</v>
+        <v>12924</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13116</v>
+        <v>13113</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -1848,120 +1848,120 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13200</v>
+        <v>13114</v>
       </c>
       <c r="B134">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13928</v>
+        <v>13116</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13962</v>
+        <v>13928</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>19687</v>
+        <v>13962</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>19980</v>
+        <v>13968</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19982</v>
+        <v>19687</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21088</v>
+        <v>19980</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21454</v>
+        <v>19982</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21793</v>
+        <v>19997</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>232</v>
+        <v>31</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21806</v>
+        <v>21088</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21810</v>
+        <v>21454</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
         <v>7</v>
@@ -1969,51 +1969,51 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22364</v>
+        <v>21793</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>22634</v>
+        <v>21806</v>
       </c>
       <c r="B146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23234</v>
+        <v>21808</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23238</v>
+        <v>21810</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24669</v>
+        <v>22364</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2024,12 +2024,45 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
+        <v>22634</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>23238</v>
+      </c>
+      <c r="B151">
+        <v>29</v>
+      </c>
+      <c r="C151">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>24669</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
         <v>25960</v>
       </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
         <v>128</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C153"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,268 +402,268 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>32</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>206</v>
+        <v>143</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>330</v>
+        <v>145</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>292</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>358</v>
+        <v>146</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>115</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>411</v>
+        <v>205</v>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>414</v>
+        <v>206</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>418</v>
+        <v>305</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>434</v>
+        <v>307</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>436</v>
+        <v>326</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>468</v>
+        <v>361</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>583</v>
+        <v>378</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>41</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>589</v>
+        <v>411</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>624</v>
+        <v>413</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>788</v>
+        <v>414</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -671,128 +671,128 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>947</v>
+        <v>417</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>976</v>
+        <v>418</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1006</v>
+        <v>434</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1055</v>
+        <v>523</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1095</v>
+        <v>583</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>236</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1134</v>
+        <v>589</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1414</v>
+        <v>788</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1429</v>
+        <v>823</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34">
-        <v>65</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1448</v>
+        <v>944</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1654</v>
+        <v>976</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1656</v>
+        <v>1006</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1814</v>
+        <v>1055</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -803,252 +803,252 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2099</v>
+        <v>1124</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2188</v>
+        <v>1134</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2190</v>
+        <v>1243</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2193</v>
+        <v>1490</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2194</v>
+        <v>1492</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2203</v>
+        <v>1504</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2212</v>
+        <v>1654</v>
       </c>
       <c r="B45">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2217</v>
+        <v>1656</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2265</v>
+        <v>2049</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>348</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2331</v>
+        <v>2050</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>59</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2419</v>
+        <v>2188</v>
       </c>
       <c r="B49">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2436</v>
+        <v>2193</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2438</v>
+        <v>2194</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>298</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2507</v>
+        <v>2203</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2805</v>
+        <v>2217</v>
       </c>
       <c r="B53">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2859</v>
+        <v>2331</v>
       </c>
       <c r="B54">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2934</v>
+        <v>2419</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C55">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2990</v>
+        <v>2422</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C56">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2992</v>
+        <v>2423</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C57">
-        <v>129</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3016</v>
+        <v>2436</v>
       </c>
       <c r="B58">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3434</v>
+        <v>2507</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3495</v>
+        <v>2912</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>523</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3598</v>
+        <v>2934</v>
       </c>
       <c r="B61">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>7</v>
@@ -1056,98 +1056,98 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3671</v>
+        <v>3016</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4232</v>
+        <v>3258</v>
       </c>
       <c r="B63">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4926</v>
+        <v>3434</v>
       </c>
       <c r="B64">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5152</v>
+        <v>3477</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5153</v>
+        <v>3495</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5490</v>
+        <v>3671</v>
       </c>
       <c r="B67">
         <v>2</v>
       </c>
       <c r="C67">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5491</v>
+        <v>3674</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>107</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5577</v>
+        <v>4926</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5584</v>
+        <v>5152</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>7</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5585</v>
+        <v>5153</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -1166,549 +1166,549 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5646</v>
+        <v>5490</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5647</v>
+        <v>5584</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5648</v>
+        <v>5585</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5649</v>
+        <v>5646</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5733</v>
+        <v>5648</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6097</v>
+        <v>6098</v>
       </c>
       <c r="B77">
         <v>80</v>
       </c>
       <c r="C77">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6098</v>
+        <v>6494</v>
       </c>
       <c r="B78">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6496</v>
+        <v>7005</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6540</v>
+        <v>7007</v>
       </c>
       <c r="B80">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>70</v>
+        <v>41</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6936</v>
+        <v>7204</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>171</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7005</v>
+        <v>7885</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7204</v>
+        <v>7886</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7520</v>
+        <v>7887</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>7885</v>
+        <v>8285</v>
       </c>
       <c r="B85">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>66</v>
+        <v>258</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>7886</v>
+        <v>8648</v>
       </c>
       <c r="B86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>68</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>7887</v>
+        <v>8674</v>
       </c>
       <c r="B87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>66</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8190</v>
+        <v>8675</v>
       </c>
       <c r="B88">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8285</v>
+        <v>8676</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>239</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8648</v>
+        <v>8756</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8675</v>
+        <v>8907</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>137</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8676</v>
+        <v>8926</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>137</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8853</v>
+        <v>8990</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C93">
-        <v>128</v>
+        <v>36</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8907</v>
+        <v>9085</v>
       </c>
       <c r="B94">
         <v>29</v>
       </c>
       <c r="C94">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8915</v>
+        <v>9356</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>75</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>8923</v>
+        <v>9357</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>8939</v>
+        <v>9358</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>8990</v>
+        <v>9493</v>
       </c>
       <c r="B98">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9085</v>
+        <v>9784</v>
       </c>
       <c r="B99">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9356</v>
+        <v>9786</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9357</v>
+        <v>9877</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C101">
-        <v>23</v>
+        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>9493</v>
+        <v>10149</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>484</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>9778</v>
+        <v>10181</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>9877</v>
+        <v>10716</v>
       </c>
       <c r="B104">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>227</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>9910</v>
+        <v>10994</v>
       </c>
       <c r="B105">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>10149</v>
+        <v>11090</v>
       </c>
       <c r="B106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>458</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>10170</v>
+        <v>11092</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>10181</v>
+        <v>11234</v>
       </c>
       <c r="B108">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>10716</v>
+        <v>11396</v>
       </c>
       <c r="B109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>10980</v>
+        <v>11402</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>10993</v>
+        <v>11687</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>25</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>10994</v>
+        <v>11689</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>154</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11090</v>
+        <v>11737</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11092</v>
+        <v>11738</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11215</v>
+        <v>11792</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11234</v>
+        <v>11812</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>87</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11396</v>
+        <v>11837</v>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>45</v>
+        <v>125</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11681</v>
+        <v>11886</v>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11685</v>
+        <v>11952</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11738</v>
+        <v>11965</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>11773</v>
+        <v>12040</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C121">
         <v>7</v>
@@ -1716,241 +1716,241 @@
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>11792</v>
+        <v>12128</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>11812</v>
+        <v>12269</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>11962</v>
+        <v>12294</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C124">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12040</v>
+        <v>12721</v>
       </c>
       <c r="B125">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12128</v>
+        <v>12764</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
-        <v>22</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12294</v>
+        <v>12923</v>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12296</v>
+        <v>12924</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12546</v>
+        <v>12979</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>12764</v>
+        <v>13114</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>355</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>12791</v>
+        <v>13200</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>387</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>12924</v>
+        <v>13928</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13113</v>
+        <v>13962</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13114</v>
+        <v>13967</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13116</v>
+        <v>13968</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>13928</v>
+        <v>19685</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>13962</v>
+        <v>20555</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>13968</v>
+        <v>20556</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>19687</v>
+        <v>20977</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>19980</v>
+        <v>21088</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C140">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>19982</v>
+        <v>21454</v>
       </c>
       <c r="B141">
         <v>2</v>
       </c>
       <c r="C141">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>19997</v>
+        <v>21806</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21088</v>
+        <v>21810</v>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,112 +1958,68 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>21454</v>
+        <v>22634</v>
       </c>
       <c r="B144">
         <v>2</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>21793</v>
+        <v>23234</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C145">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>21806</v>
+        <v>23238</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C146">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>21808</v>
+        <v>23380</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>21810</v>
+        <v>25278</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>7</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>22364</v>
+        <v>25960</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>22634</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>23238</v>
-      </c>
-      <c r="B151">
-        <v>29</v>
-      </c>
-      <c r="C151">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>24669</v>
-      </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3">
-      <c r="A153">
-        <v>25960</v>
-      </c>
-      <c r="B153">
-        <v>2</v>
-      </c>
-      <c r="C153">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,285 +396,285 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>573</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>146</v>
+        <v>305</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>159</v>
+        <v>307</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>362</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>54</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>305</v>
+        <v>361</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>307</v>
+        <v>411</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>326</v>
+        <v>434</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>361</v>
+        <v>468</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>78</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>378</v>
+        <v>523</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>411</v>
+        <v>788</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>413</v>
+        <v>823</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>414</v>
+        <v>947</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>417</v>
+        <v>976</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -682,846 +682,846 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>418</v>
+        <v>1006</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>434</v>
+        <v>1055</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>523</v>
+        <v>1095</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>154</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>583</v>
+        <v>1134</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>589</v>
+        <v>1243</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>788</v>
+        <v>1309</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>823</v>
+        <v>1448</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>944</v>
+        <v>1490</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>976</v>
+        <v>1492</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1006</v>
+        <v>1654</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1055</v>
+        <v>2188</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1124</v>
+        <v>2193</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>95</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>1134</v>
+        <v>2194</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>1243</v>
+        <v>2203</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>1490</v>
+        <v>2212</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C42">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>1492</v>
+        <v>2217</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>1504</v>
+        <v>2265</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>1654</v>
+        <v>2308</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C45">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>1656</v>
+        <v>2331</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2049</v>
+        <v>2419</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C47">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2050</v>
+        <v>2436</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>241</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2188</v>
+        <v>2507</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2193</v>
+        <v>2775</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2194</v>
+        <v>2934</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2203</v>
+        <v>2935</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2217</v>
+        <v>2990</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2331</v>
+        <v>3021</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2419</v>
+        <v>3258</v>
       </c>
       <c r="B55">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>36</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2422</v>
+        <v>3434</v>
       </c>
       <c r="B56">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2423</v>
+        <v>3495</v>
       </c>
       <c r="B57">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C57">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2436</v>
+        <v>3671</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2507</v>
+        <v>3674</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2912</v>
+        <v>3896</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C60">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2934</v>
+        <v>4043</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3016</v>
+        <v>4728</v>
       </c>
       <c r="B62">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3258</v>
+        <v>4926</v>
       </c>
       <c r="B63">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>101</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3434</v>
+        <v>5152</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>3477</v>
+        <v>5153</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>3495</v>
+        <v>5577</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>3671</v>
+        <v>5584</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>47</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>3674</v>
+        <v>5585</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>123</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>4926</v>
+        <v>5648</v>
       </c>
       <c r="B69">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5152</v>
+        <v>6097</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5153</v>
+        <v>6494</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5490</v>
+        <v>7007</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5584</v>
+        <v>7885</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5585</v>
+        <v>7886</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5646</v>
+        <v>7887</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C75">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>5648</v>
+        <v>8155</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6098</v>
+        <v>8190</v>
       </c>
       <c r="B77">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6494</v>
+        <v>8285</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>25</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7005</v>
+        <v>8674</v>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>43</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7007</v>
+        <v>8675</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>41</v>
+        <v>147</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7204</v>
+        <v>8676</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>21</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7885</v>
+        <v>8756</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>71</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7886</v>
+        <v>8853</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>73</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7887</v>
+        <v>8907</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8285</v>
+        <v>8923</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>258</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8648</v>
+        <v>8990</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>184</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8674</v>
+        <v>9085</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C87">
-        <v>146</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8675</v>
+        <v>9356</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>147</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8676</v>
+        <v>9357</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>149</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8756</v>
+        <v>9358</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>180</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8907</v>
+        <v>9493</v>
       </c>
       <c r="B91">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8926</v>
+        <v>9531</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C92">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8990</v>
+        <v>9778</v>
       </c>
       <c r="B93">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9085</v>
+        <v>9786</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9356</v>
+        <v>9841</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>404</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9357</v>
+        <v>9910</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C96">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9358</v>
+        <v>10124</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9493</v>
+        <v>10149</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>7</v>
+        <v>488</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9784</v>
+        <v>10181</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C99">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9786</v>
+        <v>10716</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>9877</v>
+        <v>10980</v>
       </c>
       <c r="B101">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>247</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10149</v>
+        <v>10994</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>484</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10181</v>
+        <v>11090</v>
       </c>
       <c r="B103">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10716</v>
+        <v>11092</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -1529,282 +1529,282 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10994</v>
+        <v>11215</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11090</v>
+        <v>11402</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11092</v>
+        <v>11687</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>161</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11234</v>
+        <v>11689</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>93</v>
+        <v>161</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11396</v>
+        <v>11737</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11402</v>
+        <v>11738</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11687</v>
+        <v>11792</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>155</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11689</v>
+        <v>11793</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>154</v>
+        <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11737</v>
+        <v>11812</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11738</v>
+        <v>11835</v>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11792</v>
+        <v>11886</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11812</v>
+        <v>11952</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11837</v>
+        <v>11965</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>125</v>
+        <v>29</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11886</v>
+        <v>12040</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C118">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>11952</v>
+        <v>12128</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>107</v>
+        <v>23</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>11965</v>
+        <v>12294</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C120">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12040</v>
+        <v>12296</v>
       </c>
       <c r="B121">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12128</v>
+        <v>12579</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12269</v>
+        <v>12764</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>35</v>
+        <v>362</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12294</v>
+        <v>12923</v>
       </c>
       <c r="B124">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12721</v>
+        <v>12924</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>146</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12764</v>
+        <v>12979</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>366</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12923</v>
+        <v>13041</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>19</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>12924</v>
+        <v>13113</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>12979</v>
+        <v>13114</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13114</v>
+        <v>13116</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -1826,18 +1826,18 @@
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13928</v>
+        <v>13962</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>24</v>
+        <v>52</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13962</v>
+        <v>13968</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -1848,87 +1848,87 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>13967</v>
+        <v>20555</v>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>13968</v>
+        <v>20556</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>19685</v>
+        <v>20977</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>20555</v>
+        <v>21088</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>20556</v>
+        <v>21454</v>
       </c>
       <c r="B138">
         <v>2</v>
       </c>
       <c r="C138">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>20977</v>
+        <v>21793</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>20</v>
+        <v>122</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21088</v>
+        <v>21806</v>
       </c>
       <c r="B140">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21454</v>
+        <v>21808</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
         <v>7</v>
@@ -1936,24 +1936,24 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21806</v>
+        <v>21810</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>21810</v>
+        <v>22364</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -1991,35 +1991,68 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23380</v>
+        <v>23332</v>
       </c>
       <c r="B147">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>25278</v>
+        <v>23380</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C148">
-        <v>145</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
+        <v>24668</v>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>24669</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>25278</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
         <v>25960</v>
       </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149">
-        <v>144</v>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C152"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,106 +396,106 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>87</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>291</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>141</v>
+        <v>107</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -528,29 +528,29 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>247</v>
+        <v>146</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>305</v>
+        <v>161</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>76</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -561,35 +561,35 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>328</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -605,57 +605,57 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>523</v>
+        <v>434</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>788</v>
+        <v>616</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>823</v>
+        <v>788</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -671,21 +671,21 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1006</v>
+        <v>976</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,7 +693,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1055</v>
+        <v>1006</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -704,13 +704,13 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1095</v>
+        <v>1055</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30">
-        <v>255</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -748,35 +748,35 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1448</v>
+        <v>1490</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1492</v>
+        <v>1504</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -792,153 +792,153 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2188</v>
+        <v>1655</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2193</v>
+        <v>1656</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2194</v>
+        <v>2049</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2203</v>
+        <v>2193</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2212</v>
+        <v>2194</v>
       </c>
       <c r="B42">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2217</v>
+        <v>2203</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2265</v>
+        <v>2217</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2308</v>
+        <v>2331</v>
       </c>
       <c r="B45">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2331</v>
+        <v>2419</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C46">
-        <v>63</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="B47">
         <v>29</v>
       </c>
       <c r="C47">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2436</v>
+        <v>2423</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C48">
-        <v>63</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2507</v>
+        <v>2436</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2775</v>
+        <v>2438</v>
       </c>
       <c r="B50">
         <v>2</v>
       </c>
       <c r="C50">
-        <v>7</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2934</v>
+        <v>2507</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -946,164 +946,164 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2935</v>
+        <v>2774</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2990</v>
+        <v>2775</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3021</v>
+        <v>2805</v>
       </c>
       <c r="B54">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="C54">
-        <v>38</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3258</v>
+        <v>2934</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>104</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3434</v>
+        <v>2990</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3495</v>
+        <v>3016</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="C57">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3671</v>
+        <v>3258</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C58">
-        <v>47</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3674</v>
+        <v>3430</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C59">
-        <v>125</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3896</v>
+        <v>3434</v>
       </c>
       <c r="B60">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4043</v>
+        <v>3495</v>
       </c>
       <c r="B61">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4728</v>
+        <v>3671</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4926</v>
+        <v>3674</v>
       </c>
       <c r="B63">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>39</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5152</v>
+        <v>3955</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5153</v>
+        <v>4926</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5577</v>
+        <v>5152</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,21 +1111,21 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5584</v>
+        <v>5153</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5585</v>
+        <v>5490</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -1133,351 +1133,351 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5648</v>
+        <v>5491</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>6097</v>
+        <v>5493</v>
       </c>
       <c r="B70">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>35</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>6494</v>
+        <v>5584</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
-        <v>26</v>
+        <v>132</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>7007</v>
+        <v>5585</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>7885</v>
+        <v>5648</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>7886</v>
+        <v>5733</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>7887</v>
+        <v>6098</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C75">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>8155</v>
+        <v>6158</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>13</v>
+        <v>135</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>8190</v>
+        <v>6494</v>
       </c>
       <c r="B77">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8285</v>
+        <v>6496</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>255</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8674</v>
+        <v>6936</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8675</v>
+        <v>7007</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>147</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8676</v>
+        <v>7204</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>149</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8756</v>
+        <v>7885</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>182</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8853</v>
+        <v>7886</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8907</v>
+        <v>7887</v>
       </c>
       <c r="B84">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C84">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8923</v>
+        <v>8155</v>
       </c>
       <c r="B85">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8990</v>
+        <v>8285</v>
       </c>
       <c r="B86">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>36</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>9085</v>
+        <v>8649</v>
       </c>
       <c r="B87">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>9356</v>
+        <v>8672</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>9</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>9357</v>
+        <v>8674</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>13</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>9358</v>
+        <v>8756</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>30</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9493</v>
+        <v>8853</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9531</v>
+        <v>8907</v>
       </c>
       <c r="B92">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C92">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9778</v>
+        <v>8915</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9786</v>
+        <v>8923</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C94">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9841</v>
+        <v>8990</v>
       </c>
       <c r="B95">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>404</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9910</v>
+        <v>9085</v>
       </c>
       <c r="B96">
         <v>29</v>
       </c>
       <c r="C96">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10124</v>
+        <v>9356</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10149</v>
+        <v>9357</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>488</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10181</v>
+        <v>9358</v>
       </c>
       <c r="B99">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10716</v>
+        <v>9493</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100">
         <v>7</v>
@@ -1485,43 +1485,43 @@
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10980</v>
+        <v>10149</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>491</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10994</v>
+        <v>10170</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11090</v>
+        <v>10181</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11092</v>
+        <v>10716</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104">
         <v>7</v>
@@ -1529,260 +1529,260 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11215</v>
+        <v>10994</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11402</v>
+        <v>11090</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11687</v>
+        <v>11092</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>161</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11689</v>
+        <v>11396</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>161</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11737</v>
+        <v>11399</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11738</v>
+        <v>11402</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11792</v>
+        <v>11685</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11793</v>
+        <v>11687</v>
       </c>
       <c r="B112">
         <v>2</v>
       </c>
       <c r="C112">
-        <v>51</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11812</v>
+        <v>11738</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11835</v>
+        <v>11773</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>129</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11886</v>
+        <v>11792</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11952</v>
+        <v>11812</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>107</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11965</v>
+        <v>11835</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>29</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12040</v>
+        <v>11886</v>
       </c>
       <c r="B118">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12128</v>
+        <v>12040</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C119">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12294</v>
+        <v>12128</v>
       </c>
       <c r="B120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12296</v>
+        <v>12269</v>
       </c>
       <c r="B121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12579</v>
+        <v>12294</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C122">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12764</v>
+        <v>12721</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123">
-        <v>362</v>
+        <v>145</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12923</v>
+        <v>12764</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
-        <v>19</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12924</v>
+        <v>12923</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12979</v>
+        <v>12924</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13041</v>
+        <v>12979</v>
       </c>
       <c r="B127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>74</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13113</v>
+        <v>13114</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -1793,164 +1793,164 @@
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13114</v>
+        <v>13200</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13116</v>
+        <v>13968</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>13200</v>
+        <v>19685</v>
       </c>
       <c r="B131">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>124</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>13962</v>
+        <v>19687</v>
       </c>
       <c r="B132">
         <v>1</v>
       </c>
       <c r="C132">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>13968</v>
+        <v>20555</v>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>52</v>
+        <v>31</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>20555</v>
+        <v>20556</v>
       </c>
       <c r="B134">
         <v>2</v>
       </c>
       <c r="C134">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>20556</v>
+        <v>20977</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>20977</v>
+        <v>21088</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C136">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21088</v>
+        <v>21454</v>
       </c>
       <c r="B137">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21454</v>
+        <v>21793</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>450</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21793</v>
+        <v>21806</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>122</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21806</v>
+        <v>21810</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21808</v>
+        <v>22364</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21810</v>
+        <v>22634</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22364</v>
+        <v>23234</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C143">
         <v>16</v>
@@ -1958,18 +1958,18 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22634</v>
+        <v>23238</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23234</v>
+        <v>23380</v>
       </c>
       <c r="B145">
         <v>29</v>
@@ -1980,78 +1980,45 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23238</v>
+        <v>24669</v>
       </c>
       <c r="B146">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23332</v>
+        <v>24670</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23380</v>
+        <v>25278</v>
       </c>
       <c r="B148">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C148">
-        <v>32</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24668</v>
+        <v>25960</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3">
-      <c r="A150">
-        <v>24669</v>
-      </c>
-      <c r="B150">
-        <v>1</v>
-      </c>
-      <c r="C150">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
-      <c r="A151">
-        <v>25278</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3">
-      <c r="A152">
-        <v>25960</v>
-      </c>
-      <c r="B152">
-        <v>2</v>
-      </c>
-      <c r="C152">
         <v>145</v>
       </c>
     </row>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,35 +396,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -435,7 +435,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -446,499 +446,499 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>567</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>754</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>142</v>
+        <v>412</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>143</v>
+        <v>470</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>79</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>144</v>
+        <v>473</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>145</v>
+        <v>788</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>146</v>
+        <v>922</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>161</v>
+        <v>936</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>305</v>
+        <v>944</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>307</v>
+        <v>949</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>76</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>326</v>
+        <v>976</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>362</v>
+        <v>1006</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>70</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>411</v>
+        <v>1055</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>413</v>
+        <v>1309</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>417</v>
+        <v>1414</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>434</v>
+        <v>1450</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>616</v>
+        <v>1560</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>101</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>788</v>
+        <v>1576</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>947</v>
+        <v>1654</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>950</v>
+        <v>1655</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>976</v>
+        <v>1656</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1006</v>
+        <v>1705</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1055</v>
+        <v>2049</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1134</v>
+        <v>2193</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1243</v>
+        <v>2194</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>1309</v>
+        <v>2203</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>1490</v>
+        <v>2217</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>1492</v>
+        <v>2331</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>1504</v>
+        <v>2418</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C36">
-        <v>83</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>1654</v>
+        <v>2497</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>46</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>1655</v>
+        <v>2504</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>1656</v>
+        <v>2507</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2049</v>
+        <v>2730</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2193</v>
+        <v>2736</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2194</v>
+        <v>2803</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2203</v>
+        <v>2934</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2217</v>
+        <v>2935</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2331</v>
+        <v>2990</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2419</v>
+        <v>2992</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2422</v>
+        <v>3073</v>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2423</v>
+        <v>3430</v>
       </c>
       <c r="B48">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>19</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2436</v>
+        <v>3434</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2438</v>
+        <v>3495</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>322</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2507</v>
+        <v>3581</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -946,21 +946,21 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2774</v>
+        <v>3582</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>85</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2775</v>
+        <v>3585</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -968,21 +968,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2805</v>
+        <v>3673</v>
       </c>
       <c r="B54">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2934</v>
+        <v>3915</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -990,120 +990,120 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2990</v>
+        <v>4068</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>92</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3016</v>
+        <v>4728</v>
       </c>
       <c r="B57">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3258</v>
+        <v>5152</v>
       </c>
       <c r="B58">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>105</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3430</v>
+        <v>5153</v>
       </c>
       <c r="B59">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3434</v>
+        <v>5243</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>46</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3495</v>
+        <v>5406</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3671</v>
+        <v>5491</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>3674</v>
+        <v>5584</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>3955</v>
+        <v>5585</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>46</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>4926</v>
+        <v>5813</v>
       </c>
       <c r="B65">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>39</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5152</v>
+        <v>5831</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,65 +1111,65 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5153</v>
+        <v>6293</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5490</v>
+        <v>6295</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5491</v>
+        <v>7885</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C69">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5493</v>
+        <v>7886</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>131</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5584</v>
+        <v>7887</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C71">
-        <v>132</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>5585</v>
+        <v>8023</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>7</v>
@@ -1177,241 +1177,241 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>5648</v>
+        <v>8285</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>29</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5733</v>
+        <v>8638</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6098</v>
+        <v>8990</v>
       </c>
       <c r="B75">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C75">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6158</v>
+        <v>9088</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C76">
-        <v>135</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>6494</v>
+        <v>9113</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>6496</v>
+        <v>9154</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6936</v>
+        <v>9487</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>7007</v>
+        <v>9493</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7204</v>
+        <v>9507</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81">
-        <v>19</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7885</v>
+        <v>9877</v>
       </c>
       <c r="B82">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C82">
-        <v>71</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>7886</v>
+        <v>9960</v>
       </c>
       <c r="B83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>73</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>7887</v>
+        <v>10150</v>
       </c>
       <c r="B84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>72</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8155</v>
+        <v>10582</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8285</v>
+        <v>10596</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>255</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8649</v>
+        <v>10598</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8672</v>
+        <v>10599</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>146</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8674</v>
+        <v>10669</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8756</v>
+        <v>10670</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>8853</v>
+        <v>10716</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>142</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>8907</v>
+        <v>10717</v>
       </c>
       <c r="B92">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>8915</v>
+        <v>11090</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>8923</v>
+        <v>11092</v>
       </c>
       <c r="B94">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -1419,131 +1419,131 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>8990</v>
+        <v>11185</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C95">
-        <v>36</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>9085</v>
+        <v>11587</v>
       </c>
       <c r="B96">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>16</v>
+        <v>406</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>9356</v>
+        <v>11619</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>9357</v>
+        <v>11737</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>9358</v>
+        <v>11773</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>9493</v>
+        <v>11794</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10149</v>
+        <v>11812</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>491</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10170</v>
+        <v>11886</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10181</v>
+        <v>11961</v>
       </c>
       <c r="B103">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10716</v>
+        <v>11962</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>10994</v>
+        <v>11967</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>7</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11090</v>
+        <v>12040</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C106">
         <v>7</v>
@@ -1551,293 +1551,293 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11092</v>
+        <v>12128</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11396</v>
+        <v>12269</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11399</v>
+        <v>12270</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11402</v>
+        <v>12294</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C110">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11685</v>
+        <v>12546</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111">
-        <v>134</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11687</v>
+        <v>12579</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11738</v>
+        <v>12611</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>30</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11773</v>
+        <v>12764</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>11792</v>
+        <v>13030</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115">
-        <v>8</v>
+        <v>154</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>11812</v>
+        <v>13041</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>11835</v>
+        <v>13113</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>11886</v>
+        <v>13117</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>98</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12040</v>
+        <v>13200</v>
       </c>
       <c r="B119">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="C119">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12128</v>
+        <v>13401</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>12269</v>
+        <v>13597</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>35</v>
+        <v>331</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>12294</v>
+        <v>13966</v>
       </c>
       <c r="B122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>12721</v>
+        <v>13968</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>145</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>12764</v>
+        <v>14037</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124">
-        <v>364</v>
+        <v>173</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>12923</v>
+        <v>19878</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>19</v>
+        <v>103</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>12924</v>
+        <v>19879</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>12979</v>
+        <v>19992</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13114</v>
+        <v>21077</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C128">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>13200</v>
+        <v>21088</v>
       </c>
       <c r="B129">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C129">
-        <v>125</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>13968</v>
+        <v>21454</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>19685</v>
+        <v>21707</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C131">
-        <v>17</v>
+        <v>278</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>19687</v>
+        <v>21745</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>20555</v>
+        <v>21752</v>
       </c>
       <c r="B133">
         <v>2</v>
@@ -1848,62 +1848,62 @@
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>20556</v>
+        <v>21773</v>
       </c>
       <c r="B134">
         <v>2</v>
       </c>
       <c r="C134">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>20977</v>
+        <v>21793</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>20</v>
+        <v>241</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21088</v>
+        <v>21806</v>
       </c>
       <c r="B136">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21454</v>
+        <v>21810</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21793</v>
+        <v>22051</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C138">
-        <v>450</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21806</v>
+        <v>22407</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -1914,76 +1914,76 @@
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21810</v>
+        <v>22573</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22364</v>
+        <v>22665</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22634</v>
+        <v>23233</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C142">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23234</v>
+        <v>23238</v>
       </c>
       <c r="B143">
         <v>29</v>
       </c>
       <c r="C143">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23238</v>
+        <v>23275</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C144">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23380</v>
+        <v>23341</v>
       </c>
       <c r="B145">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C145">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>24669</v>
+        <v>23491</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C146">
         <v>7</v>
@@ -1991,35 +1991,123 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>24670</v>
+        <v>23539</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>25278</v>
+        <v>24116</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148">
-        <v>146</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
+        <v>24121</v>
+      </c>
+      <c r="B149">
+        <v>3</v>
+      </c>
+      <c r="C149">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>24668</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>24669</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>25341</v>
+      </c>
+      <c r="B152">
+        <v>3</v>
+      </c>
+      <c r="C152">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>25699</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>25711</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155">
+        <v>25713</v>
+      </c>
+      <c r="B155">
+        <v>3</v>
+      </c>
+      <c r="C155">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
         <v>25960</v>
       </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149">
-        <v>145</v>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>26103</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,131 +396,131 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>55</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>68</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>377</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>161</v>
+        <v>336</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>370</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>192</v>
+        <v>362</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>754</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>473</v>
+        <v>788</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>788</v>
+        <v>936</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -528,18 +528,18 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>922</v>
+        <v>949</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>936</v>
+        <v>976</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -550,21 +550,21 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>944</v>
+        <v>1006</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>949</v>
+        <v>1055</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>976</v>
+        <v>1450</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>7</v>
@@ -583,230 +583,230 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1006</v>
+        <v>1560</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>118</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1055</v>
+        <v>1576</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1309</v>
+        <v>1654</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1414</v>
+        <v>1655</v>
       </c>
       <c r="B22">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1450</v>
+        <v>1705</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C23">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1560</v>
+        <v>2050</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1576</v>
+        <v>2193</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1654</v>
+        <v>2194</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1655</v>
+        <v>2203</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1656</v>
+        <v>2217</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1705</v>
+        <v>2331</v>
       </c>
       <c r="B29">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2049</v>
+        <v>2366</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30">
-        <v>278</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2193</v>
+        <v>2418</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C31">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2194</v>
+        <v>2436</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2203</v>
+        <v>2497</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2217</v>
+        <v>2504</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2331</v>
+        <v>2507</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>63</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2418</v>
+        <v>2670</v>
       </c>
       <c r="B36">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2497</v>
+        <v>2736</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>82</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2504</v>
+        <v>2934</v>
       </c>
       <c r="B38">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>294</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2507</v>
+        <v>2935</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>7</v>
@@ -814,84 +814,84 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2730</v>
+        <v>2990</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2736</v>
+        <v>2992</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2803</v>
+        <v>3073</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2934</v>
+        <v>3430</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2935</v>
+        <v>3434</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>17</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2990</v>
+        <v>3495</v>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2992</v>
+        <v>3581</v>
       </c>
       <c r="B46">
         <v>3</v>
       </c>
       <c r="C46">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3073</v>
+        <v>3582</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -902,43 +902,43 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3430</v>
+        <v>3585</v>
       </c>
       <c r="B48">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3434</v>
+        <v>3671</v>
       </c>
       <c r="B49">
         <v>2</v>
       </c>
       <c r="C49">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3495</v>
+        <v>3673</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3581</v>
+        <v>3915</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -946,43 +946,43 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>3582</v>
+        <v>4019</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3585</v>
+        <v>4063</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3673</v>
+        <v>4068</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C54">
-        <v>125</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3915</v>
+        <v>4728</v>
       </c>
       <c r="B55">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>7</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>4068</v>
+        <v>5152</v>
       </c>
       <c r="B56">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>4728</v>
+        <v>5153</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5152</v>
+        <v>5243</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>7</v>
@@ -1023,87 +1023,87 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5153</v>
+        <v>5491</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5243</v>
+        <v>5584</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5406</v>
+        <v>5585</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>76</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5491</v>
+        <v>5648</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5584</v>
+        <v>5831</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="C63">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>5585</v>
+        <v>6083</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64">
-        <v>135</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5813</v>
+        <v>6098</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C65">
-        <v>305</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5831</v>
+        <v>6293</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6293</v>
+        <v>6295</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -1122,109 +1122,109 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>6295</v>
+        <v>7885</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C68">
-        <v>8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>7885</v>
+        <v>7886</v>
       </c>
       <c r="B69">
         <v>4</v>
       </c>
       <c r="C69">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7886</v>
+        <v>7887</v>
       </c>
       <c r="B70">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>7887</v>
+        <v>8023</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>8023</v>
+        <v>8285</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>8285</v>
+        <v>8638</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>254</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8638</v>
+        <v>8990</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C74">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>8990</v>
+        <v>9088</v>
       </c>
       <c r="B75">
         <v>29</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>9088</v>
+        <v>9113</v>
       </c>
       <c r="B76">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>9113</v>
+        <v>9154</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>7</v>
@@ -1232,13 +1232,13 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9154</v>
+        <v>9374</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1271,45 +1271,45 @@
         <v>3</v>
       </c>
       <c r="C81">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9877</v>
+        <v>9960</v>
       </c>
       <c r="B82">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>240</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>9960</v>
+        <v>10150</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="C83">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>10150</v>
+        <v>10582</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>10582</v>
+        <v>10596</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -1320,35 +1320,35 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>10596</v>
+        <v>10598</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="C86">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>10598</v>
+        <v>10599</v>
       </c>
       <c r="B87">
         <v>3</v>
       </c>
       <c r="C87">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>10599</v>
+        <v>10605</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1359,7 +1359,7 @@
         <v>3</v>
       </c>
       <c r="C89">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1370,7 +1370,7 @@
         <v>3</v>
       </c>
       <c r="C90">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1397,18 +1397,18 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>11090</v>
+        <v>10993</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>11092</v>
+        <v>11090</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1419,156 +1419,156 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>11185</v>
+        <v>11092</v>
       </c>
       <c r="B95">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>11587</v>
+        <v>11396</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>406</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11619</v>
+        <v>11587</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11737</v>
+        <v>11619</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11773</v>
+        <v>11685</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11794</v>
+        <v>11687</v>
       </c>
       <c r="B100">
         <v>2</v>
       </c>
       <c r="C100">
-        <v>53</v>
+        <v>160</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11812</v>
+        <v>11689</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11886</v>
+        <v>11794</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>98</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11961</v>
+        <v>11812</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>29</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11962</v>
+        <v>11886</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>24</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11967</v>
+        <v>11961</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>12040</v>
+        <v>11967</v>
       </c>
       <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
         <v>68</v>
-      </c>
-      <c r="C106">
-        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>12128</v>
+        <v>12040</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C107">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>12269</v>
+        <v>12128</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -1579,7 +1579,7 @@
         <v>2</v>
       </c>
       <c r="C109">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -1595,384 +1595,384 @@
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12546</v>
+        <v>12304</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12579</v>
+        <v>12350</v>
       </c>
       <c r="B112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12611</v>
+        <v>12546</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12764</v>
+        <v>12579</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C114">
-        <v>382</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>13030</v>
+        <v>12611</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>154</v>
+        <v>51</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>13041</v>
+        <v>12764</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>79</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>13113</v>
+        <v>13030</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>13117</v>
+        <v>13041</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>24</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>13200</v>
+        <v>13113</v>
       </c>
       <c r="B119">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>13401</v>
+        <v>13117</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>13597</v>
+        <v>13197</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C121">
-        <v>331</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>13966</v>
+        <v>13401</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>13968</v>
+        <v>13597</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>68</v>
+        <v>660</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>14037</v>
+        <v>13966</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>173</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>19878</v>
+        <v>13968</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>103</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>19879</v>
+        <v>14037</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C126">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>19992</v>
+        <v>19879</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>21077</v>
+        <v>19992</v>
       </c>
       <c r="B128">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>21088</v>
+        <v>20966</v>
       </c>
       <c r="B129">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C129">
-        <v>13</v>
+        <v>605</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>21454</v>
+        <v>21077</v>
       </c>
       <c r="B130">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C130">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>21707</v>
+        <v>21088</v>
       </c>
       <c r="B131">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C131">
-        <v>278</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>21745</v>
+        <v>21454</v>
       </c>
       <c r="B132">
         <v>2</v>
       </c>
       <c r="C132">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>21752</v>
+        <v>21476</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C133">
-        <v>31</v>
+        <v>186</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21773</v>
+        <v>21697</v>
       </c>
       <c r="B134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C134">
-        <v>40</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21793</v>
+        <v>21745</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>241</v>
+        <v>35</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21806</v>
+        <v>21752</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21810</v>
+        <v>21773</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>22051</v>
+        <v>21806</v>
       </c>
       <c r="B138">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>22407</v>
+        <v>21810</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>22573</v>
+        <v>22051</v>
       </c>
       <c r="B140">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C140">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22665</v>
+        <v>22407</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>23233</v>
+        <v>22665</v>
       </c>
       <c r="B142">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C142">
-        <v>47</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23238</v>
+        <v>23233</v>
       </c>
       <c r="B143">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C143">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23275</v>
+        <v>23238</v>
       </c>
       <c r="B144">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C144">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23341</v>
+        <v>23275</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23491</v>
+        <v>23341</v>
       </c>
       <c r="B146">
         <v>3</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23539</v>
+        <v>23491</v>
       </c>
       <c r="B147">
         <v>3</v>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>24116</v>
+        <v>23528</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2013,18 +2013,18 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>24121</v>
+        <v>23539</v>
       </c>
       <c r="B149">
         <v>3</v>
       </c>
       <c r="C149">
-        <v>106</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24668</v>
+        <v>24116</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2035,79 +2035,134 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24669</v>
+        <v>24121</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>107</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>25341</v>
+        <v>24668</v>
       </c>
       <c r="B152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C152">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>25699</v>
+        <v>24669</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>120</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>25711</v>
+        <v>25278</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>25713</v>
+        <v>25341</v>
       </c>
       <c r="B155">
         <v>3</v>
       </c>
       <c r="C155">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>25960</v>
+        <v>25586</v>
       </c>
       <c r="B156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156">
-        <v>142</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
+        <v>25587</v>
+      </c>
+      <c r="B157">
+        <v>3</v>
+      </c>
+      <c r="C157">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>25699</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>25711</v>
+      </c>
+      <c r="B159">
+        <v>3</v>
+      </c>
+      <c r="C159">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160">
+        <v>25713</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161">
+        <v>25960</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162">
         <v>26103</v>
       </c>
-      <c r="B157">
-        <v>2</v>
-      </c>
-      <c r="C157">
-        <v>30</v>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -396,35 +396,35 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>286</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -435,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -446,125 +446,125 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>559</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>336</v>
+        <v>107</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>362</v>
+        <v>248</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>411</v>
+        <v>307</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>473</v>
+        <v>326</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>788</v>
+        <v>362</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>936</v>
+        <v>434</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>949</v>
+        <v>473</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>976</v>
+        <v>624</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>1006</v>
+        <v>788</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>121</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>1055</v>
+        <v>936</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -572,120 +572,120 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>1450</v>
+        <v>944</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1560</v>
+        <v>947</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1576</v>
+        <v>949</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1654</v>
+        <v>976</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1655</v>
+        <v>990</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1705</v>
+        <v>1055</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2050</v>
+        <v>1243</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>238</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2193</v>
+        <v>1309</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2194</v>
+        <v>1413</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2203</v>
+        <v>1414</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2217</v>
+        <v>1450</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -693,117 +693,117 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2331</v>
+        <v>1560</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2366</v>
+        <v>1576</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>159</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2418</v>
+        <v>1654</v>
       </c>
       <c r="B31">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2436</v>
+        <v>1655</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>59</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2497</v>
+        <v>2049</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2504</v>
+        <v>2169</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>297</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2507</v>
+        <v>2193</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2670</v>
+        <v>2194</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2736</v>
+        <v>2203</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2934</v>
+        <v>2216</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2935</v>
+        <v>2217</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -814,76 +814,76 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2990</v>
+        <v>2331</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2992</v>
+        <v>2366</v>
       </c>
       <c r="B41">
         <v>3</v>
       </c>
       <c r="C41">
-        <v>76</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>3073</v>
+        <v>2418</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>3430</v>
+        <v>2422</v>
       </c>
       <c r="B43">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C43">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>3434</v>
+        <v>2436</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>3495</v>
+        <v>2504</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C45">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>3581</v>
+        <v>2507</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
         <v>7</v>
@@ -891,54 +891,54 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>3582</v>
+        <v>2670</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>3585</v>
+        <v>2730</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>3671</v>
+        <v>2736</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>3673</v>
+        <v>2934</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>123</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>3915</v>
+        <v>2990</v>
       </c>
       <c r="B51">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -946,32 +946,32 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>4019</v>
+        <v>2992</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>4063</v>
+        <v>3073</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>282</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>4068</v>
+        <v>3434</v>
       </c>
       <c r="B54">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -979,21 +979,21 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>4728</v>
+        <v>3495</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>549</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>5152</v>
+        <v>3581</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>7</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5153</v>
+        <v>3582</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>7</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>5243</v>
+        <v>3585</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -1023,51 +1023,51 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>5491</v>
+        <v>3671</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>99</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>5584</v>
+        <v>3915</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>132</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5585</v>
+        <v>4063</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61">
-        <v>135</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>5648</v>
+        <v>4068</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>5831</v>
+        <v>4592</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>6083</v>
+        <v>4728</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -1089,21 +1089,21 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>6098</v>
+        <v>5152</v>
       </c>
       <c r="B65">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>6293</v>
+        <v>5153</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,54 +1111,54 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>6295</v>
+        <v>5243</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>7885</v>
+        <v>5406</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>7886</v>
+        <v>5584</v>
       </c>
       <c r="B69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>7887</v>
+        <v>5585</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>71</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>8023</v>
+        <v>5831</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -1166,51 +1166,51 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>8285</v>
+        <v>6083</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>253</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>8638</v>
+        <v>6098</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C73">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>8990</v>
+        <v>6292</v>
       </c>
       <c r="B74">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>9088</v>
+        <v>6293</v>
       </c>
       <c r="B75">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>9113</v>
+        <v>6295</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -1221,40 +1221,40 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>9154</v>
+        <v>7885</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9374</v>
+        <v>7886</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>9487</v>
+        <v>7887</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9493</v>
+        <v>8023</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -1265,51 +1265,51 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>9507</v>
+        <v>8216</v>
       </c>
       <c r="B81">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C81">
-        <v>102</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>9960</v>
+        <v>8283</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
-        <v>37</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>10150</v>
+        <v>8285</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>10</v>
+        <v>243</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>10582</v>
+        <v>8286</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>10596</v>
+        <v>8638</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -1320,76 +1320,76 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>10598</v>
+        <v>8650</v>
       </c>
       <c r="B86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>10599</v>
+        <v>8651</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>72</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>10605</v>
+        <v>8754</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>10669</v>
+        <v>8938</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>189</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>10670</v>
+        <v>8990</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>188</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>10716</v>
+        <v>9088</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C91">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>10717</v>
+        <v>9113</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -1397,18 +1397,18 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>10993</v>
+        <v>9487</v>
       </c>
       <c r="B93">
         <v>2</v>
       </c>
       <c r="C93">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>11090</v>
+        <v>9493</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -1419,43 +1419,43 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>11092</v>
+        <v>9960</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>11396</v>
+        <v>10150</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>11587</v>
+        <v>10582</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>229</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>11619</v>
+        <v>10596</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -1463,120 +1463,120 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>11685</v>
+        <v>10598</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>133</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>11687</v>
+        <v>10599</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C100">
-        <v>160</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>11689</v>
+        <v>10669</v>
       </c>
       <c r="B101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101">
-        <v>160</v>
+        <v>197</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>11794</v>
+        <v>10670</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>11812</v>
+        <v>10716</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>127</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>11886</v>
+        <v>10717</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C104">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11961</v>
+        <v>11090</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11967</v>
+        <v>11092</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>68</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>12040</v>
+        <v>11399</v>
       </c>
       <c r="B107">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>12128</v>
+        <v>11587</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>12270</v>
+        <v>11619</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
         <v>7</v>
@@ -1584,109 +1584,109 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>12294</v>
+        <v>11793</v>
       </c>
       <c r="B110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>12304</v>
+        <v>11794</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>12350</v>
+        <v>11812</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>298</v>
+        <v>132</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>12546</v>
+        <v>11838</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>7</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>12579</v>
+        <v>11886</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12611</v>
+        <v>12040</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C115">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12764</v>
+        <v>12128</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>381</v>
+        <v>23</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>13030</v>
+        <v>12294</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C117">
-        <v>103</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>13041</v>
+        <v>12304</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>13113</v>
+        <v>12579</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,238 +1694,238 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>13117</v>
+        <v>12611</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>13197</v>
+        <v>13030</v>
       </c>
       <c r="B121">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C121">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>13401</v>
+        <v>13041</v>
       </c>
       <c r="B122">
         <v>3</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>13597</v>
+        <v>13113</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>660</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>13966</v>
+        <v>13117</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>13968</v>
+        <v>13401</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C125">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>14037</v>
+        <v>13597</v>
       </c>
       <c r="B126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>173</v>
+        <v>660</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>19879</v>
+        <v>13966</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>19992</v>
+        <v>13968</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>20966</v>
+        <v>14037</v>
       </c>
       <c r="B129">
         <v>3</v>
       </c>
       <c r="C129">
-        <v>605</v>
+        <v>173</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>21077</v>
+        <v>19879</v>
       </c>
       <c r="B130">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>21088</v>
+        <v>19992</v>
       </c>
       <c r="B131">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C131">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>21454</v>
+        <v>20966</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132">
-        <v>18</v>
+        <v>606</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>21476</v>
+        <v>21077</v>
       </c>
       <c r="B133">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C133">
-        <v>186</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21697</v>
+        <v>21088</v>
       </c>
       <c r="B134">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C134">
-        <v>119</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21745</v>
+        <v>21454</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
       <c r="C135">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21752</v>
+        <v>21476</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C136">
-        <v>31</v>
+        <v>197</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21773</v>
+        <v>21697</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C137">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21806</v>
+        <v>21745</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21810</v>
+        <v>21752</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>22051</v>
+        <v>21773</v>
       </c>
       <c r="B140">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>22407</v>
+        <v>21806</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>22665</v>
+        <v>21810</v>
       </c>
       <c r="B142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142">
         <v>7</v>
@@ -1947,32 +1947,32 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>23233</v>
+        <v>22051</v>
       </c>
       <c r="B143">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C143">
-        <v>48</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>23238</v>
+        <v>22407</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>23275</v>
+        <v>22910</v>
       </c>
       <c r="B145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C145">
         <v>7</v>
@@ -1980,32 +1980,32 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>23341</v>
+        <v>23233</v>
       </c>
       <c r="B146">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C146">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23491</v>
+        <v>23275</v>
       </c>
       <c r="B147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23528</v>
+        <v>23341</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23539</v>
+        <v>23491</v>
       </c>
       <c r="B149">
         <v>3</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>24116</v>
+        <v>23528</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2035,18 +2035,18 @@
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>24121</v>
+        <v>23539</v>
       </c>
       <c r="B151">
         <v>3</v>
       </c>
       <c r="C151">
-        <v>107</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24668</v>
+        <v>24116</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2057,32 +2057,32 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>24669</v>
+        <v>24121</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>25278</v>
+        <v>24668</v>
       </c>
       <c r="B154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C154">
-        <v>141</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>25341</v>
+        <v>24669</v>
       </c>
       <c r="B155">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C155">
         <v>7</v>
@@ -2112,18 +2112,18 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>25699</v>
+        <v>25589</v>
       </c>
       <c r="B158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C158">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>25711</v>
+        <v>25591</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -2134,35 +2134,57 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>25713</v>
+        <v>25699</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C160">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>25960</v>
+        <v>25711</v>
       </c>
       <c r="B161">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C161">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
+        <v>25713</v>
+      </c>
+      <c r="B162">
+        <v>3</v>
+      </c>
+      <c r="C162">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>25960</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
         <v>26103</v>
       </c>
-      <c r="B162">
-        <v>2</v>
-      </c>
-      <c r="C162">
-        <v>22</v>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
+++ b/Pricing Logic/modules/qd_uploads/qd_cart_rules_1125.xlsx
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -402,62 +402,62 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>133</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -468,177 +468,177 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>248</v>
+        <v>114</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>54</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>307</v>
+        <v>143</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>326</v>
+        <v>159</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>45</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>70</v>
+        <v>755</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>434</v>
+        <v>206</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>473</v>
+        <v>248</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>624</v>
+        <v>307</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>788</v>
+        <v>362</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>936</v>
+        <v>411</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>944</v>
+        <v>412</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>947</v>
+        <v>414</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>949</v>
+        <v>415</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>976</v>
+        <v>417</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>990</v>
+        <v>434</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1055</v>
+        <v>473</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1243</v>
+        <v>624</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -649,54 +649,54 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1309</v>
+        <v>788</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1413</v>
+        <v>903</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C26">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1414</v>
+        <v>936</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>51</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1450</v>
+        <v>947</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1560</v>
+        <v>949</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -704,29 +704,29 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1576</v>
+        <v>976</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1654</v>
+        <v>990</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>1655</v>
+        <v>1051</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -737,186 +737,186 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2049</v>
+        <v>1055</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>277</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2169</v>
+        <v>1124</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>151</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2193</v>
+        <v>1413</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2194</v>
+        <v>1429</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2203</v>
+        <v>1450</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2216</v>
+        <v>1504</v>
       </c>
       <c r="B38">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2217</v>
+        <v>1576</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2331</v>
+        <v>1654</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>64</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2366</v>
+        <v>1655</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2418</v>
+        <v>2049</v>
       </c>
       <c r="B42">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>36</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2422</v>
+        <v>2050</v>
       </c>
       <c r="B43">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>19</v>
+        <v>467</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2436</v>
+        <v>2057</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>60</v>
+        <v>238</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2504</v>
+        <v>2169</v>
       </c>
       <c r="B45">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2507</v>
+        <v>2193</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2670</v>
+        <v>2194</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2730</v>
+        <v>2203</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2736</v>
+        <v>2217</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>7</v>
@@ -924,43 +924,43 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2934</v>
+        <v>2331</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2990</v>
+        <v>2418</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2992</v>
+        <v>2436</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>3073</v>
+        <v>2507</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>3434</v>
+        <v>2736</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>7</v>
@@ -979,29 +979,29 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>3495</v>
+        <v>2916</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>549</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>3581</v>
+        <v>2934</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>3582</v>
+        <v>2990</v>
       </c>
       <c r="B57">
         <v>3</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>3585</v>
+        <v>2992</v>
       </c>
       <c r="B58">
         <v>3</v>
@@ -1023,21 +1023,21 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3671</v>
+        <v>3257</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>3915</v>
+        <v>3434</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>7</v>
@@ -1045,21 +1045,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>4063</v>
+        <v>3495</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61">
-        <v>15</v>
+        <v>555</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4068</v>
+        <v>3581</v>
       </c>
       <c r="B62">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>7</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>4592</v>
+        <v>3582</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>4728</v>
+        <v>3671</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>5152</v>
+        <v>4068</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C65">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>5153</v>
+        <v>4728</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>7</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>5243</v>
+        <v>5152</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
         <v>7</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>5406</v>
+        <v>5243</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>7</v>
@@ -1133,18 +1133,18 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>5584</v>
+        <v>5513</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>5585</v>
+        <v>5584</v>
       </c>
       <c r="B70">
         <v>3</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>5831</v>
+        <v>5585</v>
       </c>
       <c r="B71">
         <v>3</v>
@@ -1166,54 +1166,54 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>6083</v>
+        <v>7084</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>6098</v>
+        <v>7885</v>
       </c>
       <c r="B73">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>6292</v>
+        <v>7886</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74">
-        <v>8</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6293</v>
+        <v>7887</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6295</v>
+        <v>8638</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>7</v>
@@ -1221,175 +1221,175 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7885</v>
+        <v>8650</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7886</v>
+        <v>8674</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C78">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>7887</v>
+        <v>8938</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>8023</v>
+        <v>8990</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C80">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>8216</v>
+        <v>9088</v>
       </c>
       <c r="B81">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C81">
-        <v>1068</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>8283</v>
+        <v>9113</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>243</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>8285</v>
+        <v>9207</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C83">
-        <v>243</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>8286</v>
+        <v>9208</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C84">
-        <v>239</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>8638</v>
+        <v>9209</v>
       </c>
       <c r="B85">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C85">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>8650</v>
+        <v>9239</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>92</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>8651</v>
+        <v>9487</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>8754</v>
+        <v>9493</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>178</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>8938</v>
+        <v>9507</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>8990</v>
+        <v>10150</v>
       </c>
       <c r="B90">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>9088</v>
+        <v>10582</v>
       </c>
       <c r="B91">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>9113</v>
+        <v>10596</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
         <v>7</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>9487</v>
+        <v>10598</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>9493</v>
+        <v>10669</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94">
         <v>7</v>
@@ -1419,32 +1419,32 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>9960</v>
+        <v>10670</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="C95">
-        <v>37</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>10150</v>
+        <v>10717</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>10582</v>
+        <v>11090</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>10596</v>
+        <v>11092</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>7</v>
@@ -1463,76 +1463,76 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>10598</v>
+        <v>11399</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>10599</v>
+        <v>11491</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>10669</v>
+        <v>11587</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>197</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>10670</v>
+        <v>11681</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>193</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>10716</v>
+        <v>11773</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>10717</v>
+        <v>11793</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>11090</v>
+        <v>11794</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>7</v>
@@ -1540,65 +1540,65 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>11092</v>
+        <v>11812</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>11399</v>
+        <v>11835</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>26</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>11587</v>
+        <v>11838</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>171</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>11619</v>
+        <v>11886</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>11793</v>
+        <v>11967</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>11794</v>
+        <v>12040</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C111">
         <v>7</v>
@@ -1606,43 +1606,43 @@
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>11812</v>
+        <v>12128</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>132</v>
+        <v>23</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>11838</v>
+        <v>12269</v>
       </c>
       <c r="B113">
         <v>2</v>
       </c>
       <c r="C113">
-        <v>170</v>
+        <v>67</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>11886</v>
+        <v>12294</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C114">
-        <v>128</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>12040</v>
+        <v>12304</v>
       </c>
       <c r="B115">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C115">
         <v>7</v>
@@ -1650,43 +1650,43 @@
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>12128</v>
+        <v>12579</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>12294</v>
+        <v>12611</v>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>12304</v>
+        <v>13041</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>12579</v>
+        <v>13113</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>7</v>
@@ -1694,263 +1694,263 @@
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>12611</v>
+        <v>13114</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>13030</v>
+        <v>13117</v>
       </c>
       <c r="B121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>13041</v>
+        <v>13256</v>
       </c>
       <c r="B122">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C122">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>13113</v>
+        <v>13258</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C123">
-        <v>7</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>13117</v>
+        <v>13260</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C124">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>13401</v>
+        <v>13266</v>
       </c>
       <c r="B125">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>13597</v>
+        <v>13267</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C126">
-        <v>660</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>13966</v>
+        <v>13401</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C127">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>13968</v>
+        <v>13597</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>50</v>
+        <v>661</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>14037</v>
+        <v>13928</v>
       </c>
       <c r="B129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129">
-        <v>173</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>19879</v>
+        <v>13966</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>19992</v>
+        <v>13968</v>
       </c>
       <c r="B131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>20966</v>
+        <v>14037</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132">
-        <v>606</v>
+        <v>173</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>21077</v>
+        <v>19878</v>
       </c>
       <c r="B133">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C133">
-        <v>12</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>21088</v>
+        <v>19992</v>
       </c>
       <c r="B134">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C134">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>21454</v>
+        <v>20937</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>21476</v>
+        <v>21077</v>
       </c>
       <c r="B136">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C136">
-        <v>197</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>21697</v>
+        <v>21088</v>
       </c>
       <c r="B137">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>91</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>21745</v>
+        <v>21454</v>
       </c>
       <c r="B138">
         <v>2</v>
       </c>
       <c r="C138">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>21752</v>
+        <v>21697</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C139">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>21773</v>
+        <v>21752</v>
       </c>
       <c r="B140">
         <v>2</v>
       </c>
       <c r="C140">
-        <v>80</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>21806</v>
+        <v>21773</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>21810</v>
+        <v>21806</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>22051</v>
+        <v>21810</v>
       </c>
       <c r="B143">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C143">
         <v>7</v>
@@ -1958,24 +1958,24 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>22407</v>
+        <v>22051</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C144">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>22910</v>
+        <v>22407</v>
       </c>
       <c r="B145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -1991,21 +1991,21 @@
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>23275</v>
+        <v>23491</v>
       </c>
       <c r="B147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>23341</v>
+        <v>23528</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C148">
         <v>7</v>
@@ -2013,7 +2013,7 @@
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>23491</v>
+        <v>23539</v>
       </c>
       <c r="B149">
         <v>3</v>
@@ -2024,29 +2024,29 @@
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>23528</v>
+        <v>24121</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C150">
-        <v>7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>23539</v>
+        <v>24566</v>
       </c>
       <c r="B151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>24116</v>
+        <v>24668</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2057,43 +2057,43 @@
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>24121</v>
+        <v>24669</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>109</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>24668</v>
+        <v>25278</v>
       </c>
       <c r="B154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>141</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>24669</v>
+        <v>25589</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C155">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>25586</v>
+        <v>25699</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156">
         <v>7</v>
@@ -2101,89 +2101,23 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>25587</v>
+        <v>25960</v>
       </c>
       <c r="B157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C157">
-        <v>7</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>25589</v>
+        <v>26103</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C158">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159">
-        <v>25591</v>
-      </c>
-      <c r="B159">
-        <v>3</v>
-      </c>
-      <c r="C159">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
-      <c r="A160">
-        <v>25699</v>
-      </c>
-      <c r="B160">
-        <v>2</v>
-      </c>
-      <c r="C160">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
-      <c r="A161">
-        <v>25711</v>
-      </c>
-      <c r="B161">
-        <v>3</v>
-      </c>
-      <c r="C161">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162">
-        <v>25713</v>
-      </c>
-      <c r="B162">
-        <v>3</v>
-      </c>
-      <c r="C162">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
-      <c r="A163">
-        <v>25960</v>
-      </c>
-      <c r="B163">
-        <v>2</v>
-      </c>
-      <c r="C163">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164">
-        <v>26103</v>
-      </c>
-      <c r="B164">
-        <v>2</v>
-      </c>
-      <c r="C164">
         <v>23</v>
       </c>
     </row>
